--- a/其他資料/競品分析/二手書APP競品分析.xlsx
+++ b/其他資料/競品分析/二手書APP競品分析.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2. 畢業專題\SaveMyBook\競品分析\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\其他資料\競品分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D69C8A5A-7A62-4096-8091-AC53D4808BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75953D1-8553-4179-B1FC-168707C8096C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{724E5E31-066A-430C-98BF-72C43A1203B2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{724E5E31-066A-430C-98BF-72C43A1203B2}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -36,11 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="19">
-  <si>
-    <t>項目/系統</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
   <si>
     <t>蝦皮</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -77,10 +73,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ISBN 掃描上架</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>實體智取櫃</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -113,32 +105,64 @@
   </si>
   <si>
     <t>會員等級</t>
+  </si>
+  <si>
+    <t>TAAZE讀冊生活</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>功能/平台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多元取貨方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>多元付款方式</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ISBN快速上架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Tw Cen MT"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tw Cen MT"/>
+      <name val="微軟正黑體"/>
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Tw Cen MT"/>
+      <name val="微軟正黑體"/>
       <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -165,7 +189,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -175,11 +199,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -204,9 +234,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D4EC156-AF0F-47BA-B34C-1586ED52C0FA}" name="表格3" displayName="表格3" ref="A1:J9" totalsRowShown="0">
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{65B56A6F-5E6E-47ED-8D25-0E96E7A4EF90}" name="項目/系統" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D4EC156-AF0F-47BA-B34C-1586ED52C0FA}" name="表格3" displayName="表格3" ref="A1:K11" totalsRowShown="0">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{65B56A6F-5E6E-47ED-8D25-0E96E7A4EF90}" name="功能/平台" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{4AC25BC5-9F4A-4505-8904-1ED85C69A1C8}" name="SaveMyBook"/>
     <tableColumn id="3" xr3:uid="{B5CD4BE9-4143-4AC4-905E-9C901850CFC5}" name="蝦皮"/>
     <tableColumn id="4" xr3:uid="{69899D5C-4679-4AAD-8BDE-791317A6542D}" name="臉書社團"/>
@@ -216,6 +246,7 @@
     <tableColumn id="8" xr3:uid="{B848E14C-0658-49DA-91DD-3E41C4BBF3E2}" name="Carousell_x000a_旋轉拍賣"/>
     <tableColumn id="9" xr3:uid="{53E05A76-706C-4320-9C42-B4CD51BB9777}" name="Threads"/>
     <tableColumn id="10" xr3:uid="{C12ACB15-CEC2-4793-AEFA-E75E594A1E1F}" name="Whose books_x000a_胡思二手書店"/>
+    <tableColumn id="11" xr3:uid="{318F3A4E-3969-41F2-852D-32962EEDF3BA}" name="TAAZE讀冊生活" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -444,162 +475,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C90A1371-906F-4DE9-B278-ED42B42F4E60}">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="15.4609375" defaultRowHeight="19.5" customHeight="1"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="15.5" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.4609375" style="1"/>
-    <col min="2" max="8" width="13.84375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="13.84375" customWidth="1"/>
+    <col min="1" max="1" width="15.5" style="1"/>
+    <col min="2" max="8" width="13.83203125" style="1" customWidth="1"/>
+    <col min="9" max="10" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="15.5" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="39" customHeight="1">
+    <row r="1" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A4" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A8" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/其他資料/競品分析/二手書APP競品分析.xlsx
+++ b/其他資料/競品分析/二手書APP競品分析.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\OneDrive\文件\SaveMyBook\其他資料\競品分析\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B75953D1-8553-4179-B1FC-168707C8096C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09302077-A94D-4194-BE1A-A3691033ED92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{724E5E31-066A-430C-98BF-72C43A1203B2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="23">
   <si>
     <t>蝦皮</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -656,6 +656,12 @@
       <c r="C10" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="H10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="K10" s="1" t="s">
         <v>18</v>
       </c>
@@ -665,6 +671,12 @@
         <v>21</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K11" s="1" t="s">
